--- a/template.xlsx
+++ b/template.xlsx
@@ -750,7 +750,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1039,6 +1039,7 @@
     <xf numFmtId="0" fontId="47" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1114,46 +1115,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Scheduler</author>
-  </authors>
-  <commentList>
-    <comment ref="A34" authorId="0" shapeId="0">
-      <text>
-        <t>Nurses 시트의 '오프 취향'을 얼마나 강하게 반영할지 정합니다.
-1 = 약하게 참고,  3 = 보통(기본),  4 = 강하게 반영
-다른 규칙(인원 충족, 1순위 오프)보다 우선하지는 않습니다.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Scheduler</author>
-  </authors>
-  <commentList>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>간호사가 원하는 오프 배치 방식을 적습니다. 비워두면 적용되지 않습니다.
-· 몰아 쉬기      : 오프를 3~4일씩 붙여서
-· 규칙적 오프    : 오프를 2일씩 묶어서
-· 자주 쉬기      : 오프를 하루씩 나눠서
-· 매주 수요일 오프
-· 격주 수요일 오프
-· 한 달에 한 번 금요일 오프
-두 가지를 함께 쓸 수도 있습니다.
-  예) 몰아 쉬기, 격주 수요일 오프</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1445,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X71"/>
+  <dimension ref="A1:X132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="18.125" customWidth="1" style="109" min="20" max="20"/>
@@ -1457,17 +1418,9 @@
           <t xml:space="preserve"> [근무표 자동화 스케줄러 '듀티' 사용 설명서]</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만든사람: </t>
-        </is>
-      </c>
+      <c r="K1" s="18" t="n"/>
       <c r="L1" s="19" t="n"/>
-      <c r="M1" s="56" t="inlineStr">
-        <is>
-          <t>동남보건대 간호학과 21학번 송민영</t>
-        </is>
-      </c>
+      <c r="M1" s="56" t="n"/>
       <c r="S1" s="20" t="n"/>
       <c r="T1" s="20" t="n"/>
       <c r="U1" s="20" t="n"/>
@@ -1477,11 +1430,7 @@
     </row>
     <row r="2" ht="38.25" customHeight="1" s="109">
       <c r="A2" s="13" t="n"/>
-      <c r="K2" s="23" t="inlineStr">
-        <is>
-          <t>부족한 점이 많습니다. 버그 발생시 제보해주세요 (마지막 수정 2026/05/13)</t>
-        </is>
-      </c>
+      <c r="K2" s="23" t="n"/>
       <c r="X2" s="22" t="n"/>
     </row>
     <row r="3" ht="33.75" customHeight="1" s="109" thickBot="1">
@@ -1491,11 +1440,7 @@
       <c r="G3" s="17" t="n"/>
       <c r="H3" s="17" t="n"/>
       <c r="I3" s="16" t="n"/>
-      <c r="K3" s="24" t="inlineStr">
-        <is>
-          <t>마음껏 사용해주시고 피드백, 원하는 기능, 수정해야할 점, 오류 등 알려주시면 감사하겠습니다. (alex0840@naver.com)</t>
-        </is>
-      </c>
+      <c r="K3" s="24" t="n"/>
       <c r="L3" s="25" t="n"/>
       <c r="M3" s="26" t="n"/>
       <c r="N3" s="26" t="n"/>
@@ -1651,7 +1596,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>한 달에 정확히 15개의 나이트(N)만 배정되며 나머지는 올 오프(O).</t>
+          <t>한 달에 나이트 15개가 기본이며, 근무 유형에 '나이트킵(10)'처럼 쓰면 그 개수로 조절됩니다.</t>
         </is>
       </c>
       <c r="B25" s="101" t="n"/>
@@ -1860,6 +1805,203 @@
     </row>
     <row r="71" ht="26.25" customHeight="1" s="109">
       <c r="A71" s="55" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="128" t="inlineStr">
+        <is>
+          <t>##근무 유형(Nurses 시트 4번째 칸) 쓰는 법</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>비워두면 3교대입니다. 아래 중 하나를 적어주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3교대     : D/E/N을 모두 서는 일반 간호사 (기본값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>나이트킵  : 나이트 전담. '나이트킵(10)'처럼 개수를 함께 쓸 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>데이킵    : 데이(D)만 배정</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>이브닝킵  : 이브닝(E)만 배정</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>상근      : 평일은 데이, 주말/공휴일은 오프로 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>장기휴가  : 이번 달 전체를 오프로 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="128" t="inlineStr">
+        <is>
+          <t>##차지(경력) 칸 쓰는 법 (Nurses 시트 2번째 칸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>y 또는 비워두기 : y = 모든 요일 모든 근무에서 차지 가능 / 비워두면 차지 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>특정 근무만 가능하면 : d, e   처럼 적습니다 (데이·이브닝만 차지 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>특정 요일만 가능하면 : e(금)  처럼 괄호에 요일을 적습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="128" t="inlineStr">
+        <is>
+          <t>★ 중요 : 차지 가능 인원이 너무 적으면 그 몇 명이 22~23일씩 일하게 되어 근무표가 크게 불공평해집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   매일 D·E·N 세 개 듀티마다 차지가 1명씩 필요하므로, 병동 인원의 절반 정도를 차지 가능으로 두시길 권합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="128" t="inlineStr">
+        <is>
+          <t>##오프 취향 (Nurses 시트 10번째 칸) — 신규 기능</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>간호사별로 원하는 오프 배치 방식을 적으면 규칙을 어기지 않는 선에서 반영합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>몰아 쉬기 / 규칙적 오프 / 자주 쉬기 / 매주(격주/한 달에 한 번) O요일 오프</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>반영 강도는 Setup 시트 B34에서 1~4로 조절합니다. 인원 충족과 1순위 오프를 막지는 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>참고: 나이트 뒤에는 의무 휴식 2일이 붙으므로 '자주 쉬기'라도 2일 오프가 생길 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="128" t="inlineStr">
+        <is>
+          <t>##스케줄 확정일 (Setup 시트 B33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>이미 공지한 앞부분 근무를 그대로 두고 뒷부분만 다시 짜고 싶을 때 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>예) 1-7 이라고 쓰면 1일~7일 근무는 Schedule 시트에 있는 그대로 유지하고 8일부터 새로 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="128" t="inlineStr">
+        <is>
+          <t>##벌점 점수를 읽는 법</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>점수의 절대 크기는 병동마다 달라서 의미가 없습니다. '어떤 항목이 가장 큰가'만 보시면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>보통 한 항목이 전체의 절반 이상을 차지하는데, 그 항목이 이번 근무표에서 고쳐야 할 지점입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>'격차'가 붙은 항목의 숫자는 건수가 아니라 가장 많이 한 사람과 적게 한 사람의 날짜 차이입니다.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1877,7 +2019,7 @@
   <cols>
     <col width="33.375" customWidth="1" style="109" min="1" max="1"/>
     <col width="14" customWidth="1" style="109" min="2" max="2"/>
-    <col width="22" customWidth="1" style="109" min="3" max="3"/>
+    <col width="70" customWidth="1" style="109" min="3" max="3"/>
     <col width="18" customWidth="1" style="109" min="4" max="4"/>
     <col width="17.75" customWidth="1" style="109" min="5" max="5"/>
   </cols>
@@ -2361,7 +2503,7 @@
       <c r="B33" s="100" t="n"/>
       <c r="C33" s="83" t="inlineStr">
         <is>
-          <t>## 근무표 중간을 바꾸고 싶을때만 사용합니다. 일반 근무표 작성엔 빈칸으로 두세요</t>
+          <t>◀ 이미 확정된 날짜는 다시 계산해도 그대로 유지됩니다.  예) 1-7  또는  1,2,3</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2518,7 @@
       </c>
       <c r="C34" s="103" t="inlineStr">
         <is>
-          <t>## 예) 1-20 등 날짜를 선택하고 schedule 시트의 이번달 듀티를 입력하면 20일까지의 듀티를 픽스하고 21일부터 근무표를 다시 짭니다</t>
+          <t>◀ Nurses 시트의 오프 취향을 얼마나 강하게 반영할지 (1=약하게, 3=보통, 4=강하게)</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2549,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2599,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="20" customWidth="1" style="109" min="1" max="1"/>
@@ -2612,6 +2753,7 @@
     <col width="23.75" customWidth="1" style="109" min="8" max="9"/>
     <col width="24" customWidth="1" style="109" min="10" max="10"/>
     <col width="20" customWidth="1" style="109" min="11" max="11"/>
+    <col width="52" customWidth="1" style="109" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="109">
@@ -2670,6 +2812,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="L1" s="128" t="inlineStr">
+        <is>
+          <t>◀ 오프 취향 쓰는 법 (비워두면 적용 안 함)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="124" t="inlineStr">
@@ -2680,7 +2827,7 @@
       <c r="K2" s="108" t="n"/>
       <c r="L2" s="108" t="inlineStr">
         <is>
-          <t>##설명 (작성법)</t>
+          <t>몰아 쉬기       → 오프를 3~5일씩 붙여서</t>
         </is>
       </c>
     </row>
@@ -2691,6 +2838,11 @@
         </is>
       </c>
       <c r="K3" s="101" t="n"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>규칙적 오프     → 오프를 2일씩 묶어서</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="124" t="inlineStr">
@@ -2701,7 +2853,7 @@
       <c r="K4" s="101" t="n"/>
       <c r="L4" s="108" t="inlineStr">
         <is>
-          <t>#경력 or 차지 가능 여부 : 차지를 입력하면 근무에서 적어도 1명 이상 차지가 배정됩니다.</t>
+          <t>자주 쉬기       → 오프를 하루씩 나눠서</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2866,7 @@
       <c r="K5" s="101" t="n"/>
       <c r="L5" s="101" t="inlineStr">
         <is>
-          <t>전체 차지 (모든 듀티 가능): 입력 방법: y, all, 전체, 모두 (대소문자 상관없음)</t>
+          <t>매주 수요일 오프    (월~일 아무 요일이나 가능)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2877,11 @@
         </is>
       </c>
       <c r="K6" s="116" t="n"/>
-      <c r="L6" s="101" t="n"/>
+      <c r="L6" s="101" t="inlineStr">
+        <is>
+          <t>격주 수요일 오프    (그 요일 중 절반 정도)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -2736,7 +2892,7 @@
       <c r="K7" s="116" t="n"/>
       <c r="L7" s="101" t="inlineStr">
         <is>
-          <t>부분 차지 (특정 듀티만 가능): 입력 방법: d, e, n, m 또는 한글명 (예: d, e 입력시 데이와 이브닝 근무때만 차지 가능, 한글로 "데이, 이브닝" 입력해도 가능</t>
+          <t>한 달에 한 번 금요일 오프</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2905,7 @@
       <c r="K8" s="116" t="n"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>그 외 입력 예시:</t>
+          <t>두 개를 같이 써도 됩니다 →  예) 몰아 쉬기, 격주 수요일 오프</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3284,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/template.xlsx
+++ b/template.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="49">
+  <fonts count="50">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -402,11 +402,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
-    <font/>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -448,13 +458,8 @@
         <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -743,6 +748,7 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -750,7 +756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1032,14 +1038,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1406,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X132"/>
+  <dimension ref="A1:X126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="18.125" customWidth="1" style="109" min="20" max="20"/>
@@ -1418,11 +1425,17 @@
           <t xml:space="preserve"> [근무표 자동화 스케줄러 '듀티' 사용 설명서]</t>
         </is>
       </c>
-      <c r="K1" s="18" t="n"/>
-      <c r="L1" s="19" t="n"/>
-      <c r="M1" s="56" t="n"/>
-      <c r="S1" s="20" t="n"/>
-      <c r="T1" s="20" t="n"/>
+      <c r="J1" s="125" t="n"/>
+      <c r="K1" s="125" t="n"/>
+      <c r="L1" s="125" t="n"/>
+      <c r="M1" s="125" t="n"/>
+      <c r="N1" s="125" t="n"/>
+      <c r="O1" s="125" t="n"/>
+      <c r="P1" s="125" t="n"/>
+      <c r="Q1" s="125" t="n"/>
+      <c r="R1" s="125" t="n"/>
+      <c r="S1" s="125" t="n"/>
+      <c r="T1" s="125" t="n"/>
       <c r="U1" s="20" t="n"/>
       <c r="V1" s="20" t="n"/>
       <c r="W1" s="20" t="n"/>
@@ -1430,7 +1443,17 @@
     </row>
     <row r="2" ht="38.25" customHeight="1" s="109">
       <c r="A2" s="13" t="n"/>
-      <c r="K2" s="23" t="n"/>
+      <c r="J2" s="125" t="n"/>
+      <c r="K2" s="125" t="n"/>
+      <c r="L2" s="125" t="n"/>
+      <c r="M2" s="125" t="n"/>
+      <c r="N2" s="125" t="n"/>
+      <c r="O2" s="125" t="n"/>
+      <c r="P2" s="125" t="n"/>
+      <c r="Q2" s="125" t="n"/>
+      <c r="R2" s="125" t="n"/>
+      <c r="S2" s="125" t="n"/>
+      <c r="T2" s="125" t="n"/>
       <c r="X2" s="22" t="n"/>
     </row>
     <row r="3" ht="33.75" customHeight="1" s="109" thickBot="1">
@@ -1440,16 +1463,17 @@
       <c r="G3" s="17" t="n"/>
       <c r="H3" s="17" t="n"/>
       <c r="I3" s="16" t="n"/>
-      <c r="K3" s="24" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="26" t="n"/>
-      <c r="N3" s="26" t="n"/>
-      <c r="O3" s="26" t="n"/>
-      <c r="P3" s="26" t="n"/>
-      <c r="Q3" s="26" t="n"/>
-      <c r="R3" s="26" t="n"/>
-      <c r="S3" s="26" t="n"/>
-      <c r="T3" s="26" t="n"/>
+      <c r="J3" s="125" t="n"/>
+      <c r="K3" s="125" t="n"/>
+      <c r="L3" s="125" t="n"/>
+      <c r="M3" s="125" t="n"/>
+      <c r="N3" s="125" t="n"/>
+      <c r="O3" s="125" t="n"/>
+      <c r="P3" s="125" t="n"/>
+      <c r="Q3" s="125" t="n"/>
+      <c r="R3" s="125" t="n"/>
+      <c r="S3" s="125" t="n"/>
+      <c r="T3" s="125" t="n"/>
       <c r="U3" s="26" t="n"/>
       <c r="V3" s="26" t="n"/>
       <c r="W3" s="26" t="n"/>
@@ -1462,6 +1486,17 @@
       <c r="G4" s="17" t="n"/>
       <c r="H4" s="17" t="n"/>
       <c r="I4" s="16" t="n"/>
+      <c r="J4" s="125" t="n"/>
+      <c r="K4" s="125" t="n"/>
+      <c r="L4" s="125" t="n"/>
+      <c r="M4" s="125" t="n"/>
+      <c r="N4" s="125" t="n"/>
+      <c r="O4" s="125" t="n"/>
+      <c r="P4" s="125" t="n"/>
+      <c r="Q4" s="125" t="n"/>
+      <c r="R4" s="125" t="n"/>
+      <c r="S4" s="125" t="n"/>
+      <c r="T4" s="125" t="n"/>
     </row>
     <row r="5" ht="26.25" customHeight="1" s="109">
       <c r="A5" s="14" t="inlineStr">
@@ -1469,6 +1504,17 @@
           <t xml:space="preserve">##절대 불변의 기본 규칙 </t>
         </is>
       </c>
+      <c r="J5" s="125" t="n"/>
+      <c r="K5" s="125" t="n"/>
+      <c r="L5" s="125" t="n"/>
+      <c r="M5" s="125" t="n"/>
+      <c r="N5" s="125" t="n"/>
+      <c r="O5" s="125" t="n"/>
+      <c r="P5" s="125" t="n"/>
+      <c r="Q5" s="125" t="n"/>
+      <c r="R5" s="125" t="n"/>
+      <c r="S5" s="125" t="n"/>
+      <c r="T5" s="125" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="76" t="inlineStr">
@@ -1807,197 +1853,180 @@
       <c r="A71" s="55" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="128" t="inlineStr">
+      <c r="A72" s="126" t="inlineStr">
         <is>
           <t>##근무 유형(Nurses 시트 4번째 칸) 쓰는 법</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="127" t="inlineStr">
         <is>
           <t>비워두면 3교대입니다. 아래 중 하나를 적어주세요.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="127" t="inlineStr">
         <is>
           <t>3교대     : D/E/N을 모두 서는 일반 간호사 (기본값)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="127" t="inlineStr">
         <is>
           <t>나이트킵  : 나이트 전담. '나이트킵(10)'처럼 개수를 함께 쓸 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="127" t="inlineStr">
         <is>
           <t>데이킵    : 데이(D)만 배정</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="127" t="inlineStr">
         <is>
           <t>이브닝킵  : 이브닝(E)만 배정</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="127" t="inlineStr">
         <is>
           <t>상근      : 평일은 데이, 주말/공휴일은 오프로 고정</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="127" t="inlineStr">
         <is>
           <t>장기휴가  : 이번 달 전체를 오프로 처리</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" s="127" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="128" t="inlineStr">
+      <c r="A90" s="126" t="inlineStr">
         <is>
           <t>##차지(경력) 칸 쓰는 법 (Nurses 시트 2번째 칸)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="127" t="inlineStr">
         <is>
           <t>y 또는 비워두기 : y = 모든 요일 모든 근무에서 차지 가능 / 비워두면 차지 불가</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="127" t="inlineStr">
         <is>
           <t>특정 근무만 가능하면 : d, e   처럼 적습니다 (데이·이브닝만 차지 가능)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="127" t="inlineStr">
         <is>
           <t>특정 요일만 가능하면 : e(금)  처럼 괄호에 요일을 적습니다</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" s="127" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="128" t="inlineStr">
+      <c r="A100" s="127" t="inlineStr">
         <is>
           <t>★ 중요 : 차지 가능 인원이 너무 적으면 그 몇 명이 22~23일씩 일하게 되어 근무표가 크게 불공평해집니다.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">   매일 D·E·N 세 개 듀티마다 차지가 1명씩 필요하므로, 병동 인원의 절반 정도를 차지 가능으로 두시길 권합니다.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" s="127" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="128" t="inlineStr">
-        <is>
-          <t>##오프 취향 (Nurses 시트 10번째 칸) — 신규 기능</t>
+      <c r="A106" s="126" t="inlineStr">
+        <is>
+          <t>##오프 취향 (Nurses 시트 10번째 칸)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="127" t="inlineStr">
         <is>
           <t>간호사별로 원하는 오프 배치 방식을 적으면 규칙을 어기지 않는 선에서 반영합니다.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="127" t="inlineStr">
         <is>
           <t>몰아 쉬기 / 규칙적 오프 / 자주 쉬기 / 매주(격주/한 달에 한 번) O요일 오프</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>반영 강도는 Setup 시트 B34에서 1~4로 조절합니다. 인원 충족과 1순위 오프를 막지는 않습니다.</t>
+      <c r="A112" s="127" t="inlineStr">
+        <is>
+          <t>반영 강도는 Setup 시트 B39에서 1~4로 조절합니다. 인원 충족과 1순위 오프를 막지는 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>참고: 나이트 뒤에는 의무 휴식 2일이 붙으므로 '자주 쉬기'라도 2일 오프가 생길 수 있습니다.</t>
+      <c r="A114" s="127" t="inlineStr">
+        <is>
+          <t>참고: 나이트 뒤에는 의무 휴식이 붙으므로 '자주 쉬기'라도 2일 오프가 생길 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" s="127" t="inlineStr">
+        <is>
+          <t>Note 칸은 자유 메모입니다. 무엇을 적어도 근무표에는 영향을 주지 않습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="128" t="inlineStr">
-        <is>
-          <t>##스케줄 확정일 (Setup 시트 B33)</t>
-        </is>
-      </c>
+      <c r="A118" s="127" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>이미 공지한 앞부분 근무를 그대로 두고 뒷부분만 다시 짜고 싶을 때 씁니다.</t>
+      <c r="A120" s="126" t="inlineStr">
+        <is>
+          <t>##벌점 점수를 읽는 법</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>예) 1-7 이라고 쓰면 1일~7일 근무는 Schedule 시트에 있는 그대로 유지하고 8일부터 새로 계산합니다.</t>
+      <c r="A122" s="127" t="inlineStr">
+        <is>
+          <t>점수의 절대 크기는 병동마다 달라서 의미가 없습니다. '어떤 항목이 가장 큰가'만 보시면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" s="127" t="inlineStr">
+        <is>
+          <t>보통 한 항목이 전체의 절반 이상을 차지하는데, 그 항목이 이번 근무표에서 고쳐야 할 지점입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="128" t="inlineStr">
-        <is>
-          <t>##벌점 점수를 읽는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>점수의 절대 크기는 병동마다 달라서 의미가 없습니다. '어떤 항목이 가장 큰가'만 보시면 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>보통 한 항목이 전체의 절반 이상을 차지하는데, 그 항목이 이번 근무표에서 고쳐야 할 지점입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A126" s="127" t="inlineStr">
         <is>
           <t>'격차'가 붙은 항목의 숫자는 건수가 아니라 가장 많이 한 사람과 적게 한 사람의 날짜 차이입니다.</t>
         </is>
@@ -2014,12 +2043,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="33.375" customWidth="1" style="109" min="1" max="1"/>
     <col width="14" customWidth="1" style="109" min="2" max="2"/>
-    <col width="70" customWidth="1" style="109" min="3" max="3"/>
+    <col width="22" customWidth="1" style="109" min="3" max="3"/>
     <col width="18" customWidth="1" style="109" min="4" max="4"/>
     <col width="17.75" customWidth="1" style="109" min="5" max="5"/>
   </cols>
@@ -2503,22 +2532,14 @@
       <c r="B33" s="100" t="n"/>
       <c r="C33" s="83" t="inlineStr">
         <is>
-          <t>◀ 이미 확정된 날짜는 다시 계산해도 그대로 유지됩니다.  예) 1-7  또는  1,2,3</t>
+          <t>## 근무표 중간을 바꾸고 싶을때만 사용합니다. 일반 근무표 작성엔 빈칸으로 두세요</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" s="109">
-      <c r="A34" s="125" t="inlineStr">
-        <is>
-          <t>오프 취향 반영 강도 (1~4)</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
       <c r="C34" s="103" t="inlineStr">
         <is>
-          <t>◀ Nurses 시트의 오프 취향을 얼마나 강하게 반영할지 (1=약하게, 3=보통, 4=강하게)</t>
+          <t>## 예) 1-20 등 날짜를 선택하고 schedule 시트의 이번달 듀티를 입력하면 20일까지의 듀티를 픽스하고 21일부터 근무표를 다시 짭니다</t>
         </is>
       </c>
     </row>
@@ -2540,6 +2561,21 @@
       <c r="C37" s="108" t="inlineStr">
         <is>
           <t>빈칸 : 아무것도 고정하지 않고 한 달 전체를 AI가 새로 짭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="99" t="inlineStr">
+        <is>
+          <t>오프 취향 반영 강도 (1~4)</t>
+        </is>
+      </c>
+      <c r="B39" s="128" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="129" t="inlineStr">
+        <is>
+          <t>Nurses 시트의 오프 취향을 얼마나 반영할지 (1=약하게, 3=보통, 4=강하게)</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="20" customWidth="1" style="109" min="1" max="1"/>
@@ -2752,8 +2788,8 @@
     <col width="19" customWidth="1" style="109" min="7" max="7"/>
     <col width="23.75" customWidth="1" style="109" min="8" max="9"/>
     <col width="24" customWidth="1" style="109" min="10" max="10"/>
-    <col width="20" customWidth="1" style="109" min="11" max="11"/>
-    <col width="52" customWidth="1" style="109" min="12" max="12"/>
+    <col width="18" customWidth="1" style="109" min="11" max="11"/>
+    <col width="54" customWidth="1" style="109" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="109">
@@ -2802,17 +2838,17 @@
           <t>듀티에서 제외하기</t>
         </is>
       </c>
-      <c r="J1" s="126" t="inlineStr">
+      <c r="J1" s="72" t="inlineStr">
         <is>
           <t>오프 취향(선호 패턴)</t>
         </is>
       </c>
-      <c r="K1" s="127" t="inlineStr">
+      <c r="K1" s="72" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="L1" s="128" t="inlineStr">
+      <c r="L1" s="127" t="inlineStr">
         <is>
           <t>◀ 오프 취향 쓰는 법 (비워두면 적용 안 함)</t>
         </is>
@@ -2825,9 +2861,9 @@
         </is>
       </c>
       <c r="K2" s="108" t="n"/>
-      <c r="L2" s="108" t="inlineStr">
-        <is>
-          <t>몰아 쉬기       → 오프를 3~5일씩 붙여서</t>
+      <c r="L2" s="125" t="inlineStr">
+        <is>
+          <t>몰아 쉬기        →  오프를 3~5일씩 붙여서</t>
         </is>
       </c>
     </row>
@@ -2838,9 +2874,9 @@
         </is>
       </c>
       <c r="K3" s="101" t="n"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>규칙적 오프     → 오프를 2일씩 묶어서</t>
+      <c r="L3" s="125" t="inlineStr">
+        <is>
+          <t>규칙적 오프      →  오프를 2일씩 묶어서</t>
         </is>
       </c>
     </row>
@@ -2851,9 +2887,9 @@
         </is>
       </c>
       <c r="K4" s="101" t="n"/>
-      <c r="L4" s="108" t="inlineStr">
-        <is>
-          <t>자주 쉬기       → 오프를 하루씩 나눠서</t>
+      <c r="L4" s="125" t="inlineStr">
+        <is>
+          <t>자주 쉬기        →  오프를 하루씩 나눠서</t>
         </is>
       </c>
     </row>
@@ -2864,9 +2900,9 @@
         </is>
       </c>
       <c r="K5" s="101" t="n"/>
-      <c r="L5" s="101" t="inlineStr">
-        <is>
-          <t>매주 수요일 오프    (월~일 아무 요일이나 가능)</t>
+      <c r="L5" s="125" t="inlineStr">
+        <is>
+          <t>매주 수요일 오프      (월~일 아무 요일이나 가능)</t>
         </is>
       </c>
     </row>
@@ -2877,9 +2913,9 @@
         </is>
       </c>
       <c r="K6" s="116" t="n"/>
-      <c r="L6" s="101" t="inlineStr">
-        <is>
-          <t>격주 수요일 오프    (그 요일 중 절반 정도)</t>
+      <c r="L6" s="125" t="inlineStr">
+        <is>
+          <t>격주 수요일 오프      (그 요일 중 절반 정도)</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2926,7 @@
         </is>
       </c>
       <c r="K7" s="116" t="n"/>
-      <c r="L7" s="101" t="inlineStr">
+      <c r="L7" s="125" t="inlineStr">
         <is>
           <t>한 달에 한 번 금요일 오프</t>
         </is>
@@ -2903,9 +2939,9 @@
         </is>
       </c>
       <c r="K8" s="116" t="n"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>두 개를 같이 써도 됩니다 →  예) 몰아 쉬기, 격주 수요일 오프</t>
+      <c r="L8" s="125" t="inlineStr">
+        <is>
+          <t>두 개를 같이 써도 됩니다  →  예)  몰아 쉬기, 격주 수요일 오프</t>
         </is>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -704,7 +704,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -973,6 +973,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1517,7 +1523,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
@@ -1535,7 +1540,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
@@ -1578,7 +1582,6 @@
       </c>
       <c r="B27" s="9" t="n"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
@@ -1596,9 +1599,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="26.25" customHeight="1">
       <c r="A35" s="66" t="inlineStr">
         <is>
@@ -1606,7 +1606,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
@@ -1614,7 +1613,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="21.75" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
@@ -1652,7 +1650,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
@@ -1660,7 +1657,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
@@ -1712,7 +1708,6 @@
     <row r="57">
       <c r="A57" s="68" t="n"/>
     </row>
-    <row r="58"/>
     <row r="59" ht="26.25" customHeight="1">
       <c r="A59" s="69" t="inlineStr">
         <is>
@@ -1787,7 +1782,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="106" t="inlineStr">
         <is>
@@ -1795,7 +1789,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="106" t="inlineStr">
         <is>
@@ -1803,7 +1796,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="106" t="inlineStr">
         <is>
@@ -1811,7 +1803,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="106" t="inlineStr">
         <is>
@@ -1819,7 +1810,6 @@
         </is>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="106" t="inlineStr">
         <is>
@@ -1827,7 +1817,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" s="106" t="inlineStr">
         <is>
@@ -1835,7 +1824,6 @@
         </is>
       </c>
     </row>
-    <row r="85"/>
     <row r="86">
       <c r="A86" s="106" t="inlineStr">
         <is>
@@ -1843,11 +1831,9 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="106" t="n"/>
     </row>
-    <row r="89"/>
     <row r="90" ht="26.25" customHeight="1">
       <c r="A90" s="105" t="inlineStr">
         <is>
@@ -1855,7 +1841,6 @@
         </is>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="106" t="inlineStr">
         <is>
@@ -1863,7 +1848,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="A94" s="106" t="inlineStr">
         <is>
@@ -1871,7 +1855,6 @@
         </is>
       </c>
     </row>
-    <row r="95"/>
     <row r="96">
       <c r="A96" s="106" t="inlineStr">
         <is>
@@ -1879,11 +1862,9 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="106" t="n"/>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="106" t="inlineStr">
         <is>
@@ -1891,7 +1872,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="106" t="inlineStr">
         <is>
@@ -1899,11 +1879,9 @@
         </is>
       </c>
     </row>
-    <row r="103"/>
     <row r="104">
       <c r="A104" s="106" t="n"/>
     </row>
-    <row r="105"/>
     <row r="106" ht="26.25" customHeight="1">
       <c r="A106" s="105" t="inlineStr">
         <is>
@@ -1911,7 +1889,6 @@
         </is>
       </c>
     </row>
-    <row r="107"/>
     <row r="108">
       <c r="A108" s="106" t="inlineStr">
         <is>
@@ -1919,7 +1896,6 @@
         </is>
       </c>
     </row>
-    <row r="109"/>
     <row r="110">
       <c r="A110" s="106" t="inlineStr">
         <is>
@@ -1927,7 +1903,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" s="106" t="inlineStr">
         <is>
@@ -1935,7 +1910,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="106" t="inlineStr">
         <is>
@@ -1943,7 +1917,6 @@
         </is>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" s="106" t="inlineStr">
         <is>
@@ -1951,11 +1924,9 @@
         </is>
       </c>
     </row>
-    <row r="117"/>
     <row r="118">
       <c r="A118" s="106" t="n"/>
     </row>
-    <row r="119"/>
     <row r="120" ht="26.25" customHeight="1">
       <c r="A120" s="105" t="inlineStr">
         <is>
@@ -1963,7 +1934,6 @@
         </is>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="106" t="inlineStr">
         <is>
@@ -1971,7 +1941,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" s="106" t="inlineStr">
         <is>
@@ -1979,7 +1948,6 @@
         </is>
       </c>
     </row>
-    <row r="125"/>
     <row r="126">
       <c r="A126" s="106" t="inlineStr">
         <is>
@@ -2006,6 +1974,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17.75" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2102,13 +2071,21 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n"/>
-      <c r="C7" s="56" t="n"/>
-      <c r="D7" s="56" t="n"/>
-      <c r="E7" s="56" t="n"/>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t>각 요일 별 시프트 개수를 넣어주세요</t>
+      <c r="B7" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="116" t="inlineStr">
+        <is>
+          <t>◀ 예시 숫자입니다. 반드시 병동에 맞게 고쳐 주세요.</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2095,21 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n"/>
-      <c r="C8" s="56" t="n"/>
-      <c r="D8" s="56" t="n"/>
-      <c r="E8" s="56" t="n"/>
-      <c r="G8" s="73" t="inlineStr">
-        <is>
-          <t>M은 보통 시프트&amp;미들 근무로 9 to 6 근무를 의미합니다</t>
+      <c r="B8" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   B열=데이(D)  C열=이브닝(E)  D열=나이트(N)  E열=미들(M)</t>
         </is>
       </c>
     </row>
@@ -2134,11 +2119,23 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n"/>
-      <c r="C9" s="56" t="n"/>
-      <c r="D9" s="56" t="n"/>
-      <c r="E9" s="56" t="n"/>
-      <c r="G9" s="2" t="n"/>
+      <c r="B9" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   하루에 각 근무마다 몇 명이 필요한지 적습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="61" t="inlineStr">
@@ -2146,11 +2143,23 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B10" s="56" t="n"/>
-      <c r="C10" s="56" t="n"/>
-      <c r="D10" s="56" t="n"/>
-      <c r="E10" s="56" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="B10" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   미들 근무를 쓰지 않는 병동은 E열을 0으로 두세요.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="61" t="inlineStr">
@@ -2158,10 +2167,18 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B11" s="56" t="n"/>
-      <c r="C11" s="56" t="n"/>
-      <c r="D11" s="56" t="n"/>
-      <c r="E11" s="56" t="n"/>
+      <c r="B11" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="56" t="n">
+        <v>0</v>
+      </c>
       <c r="G11" s="2" t="n"/>
     </row>
     <row r="12">
@@ -2170,10 +2187,18 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B12" s="56" t="n"/>
-      <c r="C12" s="56" t="n"/>
-      <c r="D12" s="56" t="n"/>
-      <c r="E12" s="56" t="n"/>
+      <c r="B12" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="56" t="n">
+        <v>0</v>
+      </c>
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
@@ -2182,10 +2207,18 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B13" s="56" t="n"/>
-      <c r="C13" s="56" t="n"/>
-      <c r="D13" s="56" t="n"/>
-      <c r="E13" s="56" t="n"/>
+      <c r="B13" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A14" s="23" t="n"/>
